--- a/TestData/CorporateWellnessData.xlsx
+++ b/TestData/CorporateWellnessData.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
-        <v>FAIL</v>
+        <v>ERROR</v>
       </c>
     </row>
     <row r="5">

--- a/TestData/CorporateWellnessData.xlsx
+++ b/TestData/CorporateWellnessData.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
-        <v>ERROR</v>
+        <v>FAIL</v>
       </c>
     </row>
     <row r="5">
